--- a/rubric_template.xlsx
+++ b/rubric_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1420" yWindow="760" windowWidth="27980" windowHeight="18360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1480" yWindow="760" windowWidth="27920" windowHeight="18360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -51,7 +51,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -64,6 +64,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,13 +465,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="10.83203125" customWidth="1" style="2" min="1" max="2"/>
+    <col width="10.83203125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="17.6640625" customWidth="1" style="2" min="2" max="2"/>
     <col width="20.83203125" customWidth="1" style="2" min="3" max="7"/>
-    <col width="10.83203125" customWidth="1" style="2" min="8" max="8"/>
-    <col width="10.83203125" customWidth="1" style="2" min="9" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="2" min="8" max="9"/>
+    <col width="10.83203125" customWidth="1" style="2" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="1">
@@ -494,41 +498,41 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>N Courses</t>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Undergrad GPA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A large, robust sample (15+ courses) providing high confidence in the GPA. Typical of a student finishing undergrad or well into a course-heavy program.</t>
+          <t>GPA 95%+ — exceptional</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A solid sample (10–14 courses) offering good confidence in the GPA.</t>
+          <t>GPA 88–94% — strong</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A moderate sample (5–9 courses); GPA should be interpreted with some caution.</t>
+          <t>GPA 84–87% — solid</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A small sample (2–4 courses), such as a few graduate courses. GPA may not be representative of sustained academic performance.</t>
+          <t>GPA 80–83% — meets the typical minimum for competitive graduate applicants</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0–1 courses recorded — insufficient data to draw meaningful conclusions from the GPA.</t>
+          <t>GPA &lt; 80% — below the expected threshold</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>GPA</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Master's GPA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -557,335 +561,367 @@
         </is>
       </c>
     </row>
-    <row r="4" customFormat="1" s="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Scholarship</t>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PhD GPA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GPA 95%+ — exceptional</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GPA 88–94% — strong</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GPA 84–87% — solid</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>GPA 80–83% — meets the typical minimum for competitive graduate applicants</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>GPA &lt; 80% — below the expected threshold</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Publications</t>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Academic Awards</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cumulative IREI ≥ 6. Multiple first-author papers in good journals, or one exceptional paper in a top-tier journal. Demonstrates a strong, externally validated publication record relative to the field.</t>
+          <t>Multiple competitive external scholarships from government or professional agencies (e.g., NSERC, OGS), or a high-value internal merit scholarship, with repeated Dean's List appearances. Strong, sustained external validation of academic excellence.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cumulative IREI 3–5.9. One solid first-author paper in a good journal, possibly supplemented by co-author contributions. Clear evidence of meaningful participation in the research publication process.</t>
+          <t>At least one competitive external or high-value internal merit scholarship, or consistent Dean's List recognition (two or more times). Clear academic distinction recognized beyond course grades alone.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cumulative IREI 1–2.9. One modest first-author paper in a lower-impact venue, or several middle- or last-author contributions. Some publication experience but limited demonstrated independence.</t>
+          <t>A single Dean's List appearance, or one internal merit-based scholarship of moderate value with a genuine competitive component. Some formal recognition of academic merit, but limited in scope or frequency.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cumulative IREI 0.1–0.9. Only middle-author contributions, preprints, or publications in very low-impact venues. Minimal evidence of a substantive publication record.</t>
+          <t>A one-time entrance award granted at admission, or a single minor bursary with limited merit criteria. Recognized upon entry rather than for sustained academic performance.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cumulative IREI = 0. No publications of any kind reported.</t>
+          <t>No academic awards, scholarships, or formal recognitions of any kind reported.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Other Contributions</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Multiple high-profile contributions across diverse formats — e.g., book chapter in a reputable edited volume, invited editorial or opinion piece in a major journal or magazine, patent filing, featured interview in a national or international science/trade outlet, or a widely-read technical report for a government or industry body. Demonstrates broad reach and recognition by the wider community.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>One or more notable non-refereed contributions (e.g., book chapter, technical or government report, book review in a peer-reviewed journal, interview or feature in a recognized publication, white paper or policy brief). Shows meaningful engagement with science communication beyond standard peer-reviewed publishing.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Some non-refereed output with limited reach (e.g., article in a departmental or trade newsletter, opinion piece in a student or local publication, contribution to a collaborative white paper, popular science blog). Genuine effort at broader communication but limited external impact or recognition.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Minimal or informal science communication — e.g., a single blog post, social media science content, or a minor contribution to a collaborative document. Little evidence of sustained or deliberate engagement with non-traditional outputs.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>No non-refereed outputs or alternative forms of science communication reported.</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Research</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Conferences</t>
+          <t>Publications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Personally delivered an oral presentation at a major international conference (e.g., AIChE Annual Meeting, ACS, Gordon Research Conference). Or multiple self-presented contributions (talks or posters) across national and international venues. The applicant is the presenter of record, not a co-author whose supervisor presented on their behalf.</t>
+          <t>Cumulative IREI ≥ 6. Multiple first-author papers in good journals, or one exceptional paper in a top-tier journal. Demonstrates a strong, externally validated publication record relative to the field.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Self-presented a poster at a major international conference, or delivered an oral talk at a national conference. Demonstrates ability to represent their work to a broad scientific audience. May include multiple poster presentations at national-level events.</t>
+          <t>Cumulative IREI 3–5.9. One solid first-author paper in a good journal, possibly supplemented by co-author contributions. Clear evidence of meaningful participation in the research publication process.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Presented a poster or gave a talk at a local or campus-level conference (e.g., departmental symposium, university research day), or contributed to a national/international conference without personally presenting (e.g., listed as co-author while supervisor delivered the presentation).</t>
+          <t>Cumulative IREI 1–2.9. One modest first-author paper in a lower-impact venue, or several middle- or last-author contributions. Some publication experience but limited demonstrated independence.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Attended one or more conferences without any presentation role, or contributed to a campus event in a very minor capacity (e.g., helped organize but did not present).</t>
+          <t>Cumulative IREI 0.1–0.9. Only middle-author contributions, preprints, or publications in very low-impact venues. Minimal evidence of a substantive publication record.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No conference participation of any kind reported.</t>
+          <t>Cumulative IREI = 0. No publications of any kind reported.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Work Experience</t>
+          <t>Other Contributions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Substantial research experience in a high-quality setting — multiple co-op terms, an extended internship (e.g., 16+ months), or an international research visit, in a university lab, industrial R&amp;D department, or national research facility (e.g., NRC). Demonstrates ability to function independently in a research environment. Combinations of the above (e.g., co-op plus a research visit abroad) are particularly strong.</t>
+          <t>Multiple high-profile contributions across diverse formats — e.g., book chapter in a reputable edited volume, invited editorial or opinion piece in a major journal or magazine, patent filing, featured interview in a national or international science/trade outlet, or a widely-read technical report for a government or industry body. Demonstrates broad reach and recognition by the wider community.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>At least one meaningful research position (e.g., one or two co-op terms, a summer research assistantship, a shorter industrial R&amp;D placement, or a research visit abroad), showing genuine exposure to research practice. May be complemented by non-research technical roles or a study abroad term. A solid foundation even if not as extensive as a 4.</t>
+          <t>One or more notable non-refereed contributions (e.g., book chapter, technical or government report, book review in a peer-reviewed journal, interview or feature in a recognized publication, white paper or policy brief). Shows meaningful engagement with science communication beyond standard peer-reviewed publishing.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Work experience primarily in industry but outside of research (e.g., technical engineering, quality control, operations), or a single brief research exposure alongside non-technical work. Study abroad for coursework only also falls here. Shows professionalism and some technical grounding but limited direct research exposure.</t>
+          <t>Some non-refereed output with limited reach (e.g., article in a departmental or trade newsletter, opinion piece in a student or local publication, contribution to a collaborative white paper, popular science blog). Genuine effort at broader communication but limited external impact or recognition.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Work experience limited to non-technical roles (e.g., retail, food service, sales). Demonstrates work ethic and responsibility but provides no insight into research aptitude or technical ability.</t>
+          <t>Minimal or informal science communication — e.g., a single blog post, social media science content, or a minor contribution to a collaborative document. Little evidence of sustained or deliberate engagement with non-traditional outputs.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No work experience of any kind reported. A concern for graduate school readiness, suggesting limited initiative or professional development outside of coursework.</t>
+          <t>No non-refereed outputs or alternative forms of science communication reported.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Recomendation Letters</t>
+          <t>Conferences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>All or most letters are from direct research supervisors who observed the applicant in a hands-on research setting. Letters speak specifically to intellectual curiosity, independence, problem-solving, and research potential, with concrete examples. Referees are credible academic sources who can meaningfully compare the applicant to peers.</t>
+          <t>Personally delivered an oral presentation at a major international conference (e.g., AIChE Annual Meeting, ACS, Gordon Research Conference). Or multiple self-presented contributions (talks or posters) across national and international venues. The applicant is the presenter of record, not a co-author whose supervisor presented on their behalf.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>At least one strong letter from a research supervisor, complemented by letters from academic instructors or thesis co-supervisors. The overall picture speaks clearly to research aptitude, even if not all referees had direct research oversight. Letters are substantive and specific rather than formulaic.</t>
+          <t>Self-presented a poster at a major international conference, or delivered an oral talk at a national conference. Demonstrates ability to represent their work to a broad scientific audience. May include multiple poster presentations at national-level events.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Letters are primarily from course instructors or a supervisor with only brief research contact. Academic ability is evident but research potential is inferred rather than directly observed. May include one industry letter; collectively the letters offer a partial picture of research readiness.</t>
+          <t>Presented a poster or gave a talk at a local or campus-level conference (e.g., departmental symposium, university research day), or contributed to a national/international conference without personally presenting (e.g., listed as co-author while supervisor delivered the presentation).</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Letters are mainly from industry employers, instructors with limited personal interaction, or non-academic supervisors. Content focuses on professional conduct or soft skills rather than intellectual or research ability. Little basis for evaluating graduate-level research potential.</t>
+          <t>Attended one or more conferences without any presentation role, or contributed to a campus event in a very minor capacity (e.g., helped organize but did not present).</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No letters provided, letters are entirely from non-academic or personal references, or the content is too generic to offer meaningful insight into the applicant’s potential.</t>
+          <t>No conference participation of any kind reported.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>Work Experience</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Substantial research experience in a high-quality setting — multiple co-op terms, an extended internship (e.g., 16+ months), or an international research visit, in a university lab, industrial R&amp;D department, or national research facility (e.g., NRC). Demonstrates ability to function independently in a research environment. Combinations of the above (e.g., co-op plus a research visit abroad) are particularly strong.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>At least one meaningful research position (e.g., one or two co-op terms, a summer research assistantship, a shorter industrial R&amp;D placement, or a research visit abroad), showing genuine exposure to research practice. May be complemented by non-research technical roles or a study abroad term. A solid foundation even if not as extensive as a 4.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Work experience primarily in industry but outside of research (e.g., technical engineering, quality control, operations), or a single brief research exposure alongside non-technical work. Study abroad for coursework only also falls here. Shows professionalism and some technical grounding but limited direct research exposure.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Work experience limited to non-technical roles (e.g., retail, food service, sales). Demonstrates work ethic and responsibility but provides no insight into research aptitude or technical ability.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No work experience of any kind reported. A concern for graduate school readiness, suggesting limited initiative or professional development outside of coursework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Recomendation Letters</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>All or most letters are from direct research supervisors who observed the applicant in a hands-on research setting. Letters speak specifically to intellectual curiosity, independence, problem-solving, and research potential, with concrete examples. Referees are credible academic sources who can meaningfully compare the applicant to peers.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>At least one strong letter from a research supervisor, complemented by letters from academic instructors or thesis co-supervisors. The overall picture speaks clearly to research aptitude, even if not all referees had direct research oversight. Letters are substantive and specific rather than formulaic.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Letters are primarily from course instructors or a supervisor with only brief research contact. Academic ability is evident but research potential is inferred rather than directly observed. May include one industry letter; collectively the letters offer a partial picture of research readiness.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Letters are mainly from industry employers, instructors with limited personal interaction, or non-academic supervisors. Content focuses on professional conduct or soft skills rather than intellectual or research ability. Little basis for evaluating graduate-level research potential.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No letters provided, letters are entirely from non-academic or personal references, or the content is too generic to offer meaningful insight into the applicant’s potential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>Research Awards</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Multiple research awards, or one highly prestigious recognition with broad scope (e.g., best thesis at faculty or university level, best paper/talk at a major international conference, highly cited or featured publication, professional society student award such as AIChE or IEEE, national research competition win, top placing in a major multi-year student engineering program such as EcoCAR). Strong external validation of research excellence.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>At least one notable research award (e.g., best poster at a regional or institutional conference, capstone design award, departmental research prize, competitive undergraduate research fellowship such as NSERC USRA, industry-sponsored design competition, hackathon win, or meaningful contribution to a competitive student team such as EcoCAR). Recognized by an external body for a meaningful research or design contribution.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Minor or local research recognition — e.g., honorable mention in a poster competition, runner-up in a capstone or design challenge, participation in a hackathon or student engineering team without a podium finish, selection for a competitive but informal research program. Some external validation but limited in prestige or scope.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Participated in award-eligible activities (conferences, capstone projects, hackathons, research programs) without receiving formal recognition. Or recognition is entirely internal — e.g., acknowledged by a supervisor but no formal award conferred.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>No research awards, prizes, or formal recognitions of any kind.</t>
         </is>
       </c>
     </row>
-    <row r="11" customFormat="1" s="1">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>N Terms</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>≤ 3 terms — weight 1.5× applied to Publications, Other Contributions, Conferences, and Research Awards</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4–5 terms — weight 1.25×</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>6–7 terms — weight 1.0× (baseline)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>8–10 terms — weight 0.85×</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>&gt; 10 terms — weight 0.75×</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Leadership</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Volunteer</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Sustained, high-impact volunteer leadership across multiple activities (e.g., international development projects, founding or leading a student association, organizing a major conference track). Significant time commitment (years, not one-offs) and demonstrable community or societal impact.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Active volunteer role(s) with clear responsibility and moderate-to-high impact (e.g., executive member of a university student society, organizing committee for a symposium or workshop, leading a local community program). Consistent engagement over at least one academic year.</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Participation in volunteer activities with some leadership or organizational responsibility (e.g., student council member, recurring club events, committee membership). Limited scope or shorter duration, but genuine contribution beyond simply attending.</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Minimal or irregular volunteer involvement — occasional participation with little responsibility or impact (e.g., helping at one-off events, passive club membership). Activities are low-stakes and require little time commitment.</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>No volunteer or extracurricular activities reported.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Additional</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Exceptional breadth or depth of extracurricular engagement. High achievement in at least one area (e.g., competitive athlete at provincial/national level, founded a functioning startup or social enterprise, significant artistic or creative accomplishment). Sustained, multi-year commitment with demonstrable outcomes.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Meaningful involvement in one or more extracurricular areas beyond volunteering, showing real dedication (e.g., active competitive sport, launched a side project or small business, consistent participation in arts, music, or cultural activities). Goes beyond casual participation.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Some extracurricular activity with moderate engagement (e.g., recreational sport, hobbyist creative work, early-stage entrepreneurial interest, participation in cultural or faith-based groups). Enjoyable but limited in scope, impact, or duration.</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Minimal extracurricular involvement outside of volunteering — one or two low-commitment activities with no notable achievement or sustained engagement.</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>No extracurricular activities outside those captured in other categories.</t>
+          <t>Volunteer</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Sustained, high-impact volunteer leadership across multiple activities (e.g., international development projects, founding or leading a student association, organizing a major conference track). Significant time commitment (years, not one-offs) and demonstrable community or societal impact.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Active volunteer role(s) with clear responsibility and moderate-to-high impact (e.g., executive member of a university student society, organizing committee for a symposium or workshop, leading a local community program). Consistent engagement over at least one academic year.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Participation in volunteer activities with some leadership or organizational responsibility (e.g., student council member, recurring club events, committee membership). Limited scope or shorter duration, but genuine contribution beyond simply attending.</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Minimal or irregular volunteer involvement — occasional participation with little responsibility or impact (e.g., helping at one-off events, passive club membership). Activities are low-stakes and require little time commitment.</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>No volunteer or extracurricular activities reported.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Non-Academic Awards</t>
+          <t>Extra-curriculars</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Exceptional breadth or depth of extracurricular engagement. High achievement in at least one area (e.g., competitive athlete at provincial/national level, founded a functioning startup or social enterprise, significant artistic or creative accomplishment). Sustained, multi-year commitment with demonstrable outcomes.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Meaningful involvement in one or more extracurricular areas beyond volunteering, showing real dedication (e.g., active competitive sport, launched a side project or small business, consistent participation in arts, music, or cultural activities). Goes beyond casual participation.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Some extracurricular activity with moderate engagement (e.g., recreational sport, hobbyist creative work, early-stage entrepreneurial interest, participation in cultural or faith-based groups). Enjoyable but limited in scope, impact, or duration.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Minimal extracurricular involvement outside of volunteering — one or two low-commitment activities with no notable achievement or sustained engagement.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No extracurricular activities outside those captured in other categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Non-Academic Accomplishments</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Multiple prestigious non-academic awards and/or highly demanding certifications (e.g., national-level athletic recognition, significant civic or community award, pilot's license, advanced professional certification requiring substantial training and demonstrated competency). Strong external validation of excellence.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>One or more notable non-academic awards or certifications of meaningful difficulty (e.g., regional sports award, community recognition, lifeguarding certification, advanced first aid, trade or professional certification). Clear evidence of skill or achievement recognized by an external body.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Some non-academic recognition or entry-level certification (e.g., local or club-level award, standard first aid/CPR, completion of a structured skills course). Genuine achievement but limited in prestige or difficulty.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Minimal non-academic accomplishments — a single low-level certification or informal recognition with little demonstrated effort or external validation (e.g., short online course certificate, minor local recognition).</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>No non-academic awards, certifications, or accomplishments reported.</t>
         </is>
